--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA400"/>
+  <dimension ref="A1:AA402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -43309,6 +43309,192 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>The Guild Collective Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>The Guild Collective Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>122487</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>Shaw Centre, 1 Scotts Road, Orchard</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>228208</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theguildcollective.com</t>
+        </is>
+      </c>
+      <c r="J401" s="2" t="inlineStr"/>
+      <c r="K401" s="2" t="inlineStr"/>
+      <c r="L401" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M401" s="2" t="inlineStr"/>
+      <c r="N401" s="2" t="inlineStr">
+        <is>
+          <t>hello@theguildcollective.com</t>
+        </is>
+      </c>
+      <c r="O401" s="2" t="inlineStr"/>
+      <c r="P401" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q401" s="2" t="inlineStr">
+        <is>
+          <t>201906364W</t>
+        </is>
+      </c>
+      <c r="R401" s="2" t="inlineStr"/>
+      <c r="S401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineWhiskySpiritsSG/</t>
+        </is>
+      </c>
+      <c r="T401" s="2" t="inlineStr"/>
+      <c r="U401" s="2" t="inlineStr"/>
+      <c r="V401" s="2" t="inlineStr"/>
+      <c r="W401" s="2" t="inlineStr">
+        <is>
+          <t>Rick</t>
+        </is>
+      </c>
+      <c r="X401" s="2" t="inlineStr">
+        <is>
+          <t>Founder And Resident Sommelier</t>
+        </is>
+      </c>
+      <c r="Y401" s="2" t="inlineStr"/>
+      <c r="Z401" s="2" t="inlineStr"/>
+      <c r="AA401" s="2" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>Our Wine Coterie Llp</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>Our Wine Coterie Llp</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>122470</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>39 Woodlands Close, Woodlands</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>737856</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>https://owc-eshop.com, https://www.ourwinecoterie.com</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr"/>
+      <c r="K402" s="2" t="inlineStr"/>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="inlineStr"/>
+      <c r="N402" s="2" t="inlineStr">
+        <is>
+          <t>enquiry@ourwinecoterie.com</t>
+        </is>
+      </c>
+      <c r="O402" s="2" t="inlineStr"/>
+      <c r="P402" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q402" s="2" t="inlineStr">
+        <is>
+          <t>T18LL1895E</t>
+        </is>
+      </c>
+      <c r="R402" s="2" t="inlineStr"/>
+      <c r="S402" s="2" t="inlineStr"/>
+      <c r="T402" s="2" t="inlineStr"/>
+      <c r="U402" s="2" t="inlineStr"/>
+      <c r="V402" s="2" t="inlineStr"/>
+      <c r="W402" s="2" t="inlineStr">
+        <is>
+          <t>Samuel Koh</t>
+        </is>
+      </c>
+      <c r="X402" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y402" s="2" t="inlineStr"/>
+      <c r="Z402" s="2" t="inlineStr"/>
+      <c r="AA402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/samkohyn/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA402"/>
+  <dimension ref="A1:AA407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -43495,6 +43495,475 @@
         </is>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>Finedrops Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>Finedrops Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>55904</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>66 Sungei Kadut Loop, Sungei Kadut</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>729503</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>https://finedrops.sg</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr"/>
+      <c r="K403" s="2" t="inlineStr"/>
+      <c r="L403" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M403" s="2" t="inlineStr"/>
+      <c r="N403" s="2" t="inlineStr">
+        <is>
+          <t>office@finedrops.sg</t>
+        </is>
+      </c>
+      <c r="O403" s="2" t="inlineStr"/>
+      <c r="P403" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q403" s="2" t="inlineStr">
+        <is>
+          <t>201806216W</t>
+        </is>
+      </c>
+      <c r="R403" s="2" t="inlineStr"/>
+      <c r="S403" s="2" t="inlineStr"/>
+      <c r="T403" s="2" t="inlineStr"/>
+      <c r="U403" s="2" t="inlineStr"/>
+      <c r="V403" s="2" t="inlineStr"/>
+      <c r="W403" s="2" t="inlineStr"/>
+      <c r="X403" s="2" t="inlineStr"/>
+      <c r="Y403" s="2" t="inlineStr"/>
+      <c r="Z403" s="2" t="inlineStr"/>
+      <c r="AA403" s="2" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>Hai Choo Wines &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>Hai Choo Wines &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>11804</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>48 Toh Guan Road East, Clementi</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>608586</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>https://hai-choo-wines-spirits.fairmart.app, https://hcwines.com</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr"/>
+      <c r="K404" s="2" t="inlineStr"/>
+      <c r="L404" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M404" s="2" t="inlineStr"/>
+      <c r="N404" s="2" t="inlineStr">
+        <is>
+          <t>sales@hcwines.com</t>
+        </is>
+      </c>
+      <c r="O404" s="2" t="inlineStr">
+        <is>
+          <t>+65 6515 6538</t>
+        </is>
+      </c>
+      <c r="P404" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q404" s="2" t="inlineStr">
+        <is>
+          <t>37556200A</t>
+        </is>
+      </c>
+      <c r="R404" s="2" t="inlineStr"/>
+      <c r="S404" s="2" t="inlineStr"/>
+      <c r="T404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winingwithhc/</t>
+        </is>
+      </c>
+      <c r="U404" s="2" t="inlineStr"/>
+      <c r="V404" s="2" t="inlineStr"/>
+      <c r="W404" s="2" t="inlineStr">
+        <is>
+          <t>Kelvin Tan</t>
+        </is>
+      </c>
+      <c r="X404" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y404" s="2" t="inlineStr"/>
+      <c r="Z404" s="2" t="inlineStr"/>
+      <c r="AA404" s="2" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/in/kelvin-tan-a040891</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>Hai Choo Wines &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>Hai Choo Wines &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>11804</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>48 Toh Guan Road East, Clementi</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>608586</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>https://hai-choo-wines-spirits.fairmart.app, https://hcwines.com</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr"/>
+      <c r="K405" s="2" t="inlineStr"/>
+      <c r="L405" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M405" s="2" t="inlineStr"/>
+      <c r="N405" s="2" t="inlineStr">
+        <is>
+          <t>sales@hcwines.com</t>
+        </is>
+      </c>
+      <c r="O405" s="2" t="inlineStr">
+        <is>
+          <t>+65 6515 6538</t>
+        </is>
+      </c>
+      <c r="P405" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q405" s="2" t="inlineStr">
+        <is>
+          <t>37556200A</t>
+        </is>
+      </c>
+      <c r="R405" s="2" t="inlineStr"/>
+      <c r="S405" s="2" t="inlineStr"/>
+      <c r="T405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winingwithhc/</t>
+        </is>
+      </c>
+      <c r="U405" s="2" t="inlineStr"/>
+      <c r="V405" s="2" t="inlineStr"/>
+      <c r="W405" s="2" t="inlineStr">
+        <is>
+          <t>Terence Goh</t>
+        </is>
+      </c>
+      <c r="X405" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y405" s="2" t="inlineStr"/>
+      <c r="Z405" s="2" t="inlineStr"/>
+      <c r="AA405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/terence-goh-478983163/</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>The Guild Collective Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>The Guild Collective Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>122487</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>Shaw Centre, 1 Scotts Road, Orchard</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>228208</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theguildcollective.com</t>
+        </is>
+      </c>
+      <c r="J406" s="2" t="inlineStr"/>
+      <c r="K406" s="2" t="inlineStr"/>
+      <c r="L406" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M406" s="2" t="inlineStr"/>
+      <c r="N406" s="2" t="inlineStr">
+        <is>
+          <t>hello@theguildcollective.com</t>
+        </is>
+      </c>
+      <c r="O406" s="2" t="inlineStr"/>
+      <c r="P406" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q406" s="2" t="inlineStr">
+        <is>
+          <t>201906364W</t>
+        </is>
+      </c>
+      <c r="R406" s="2" t="inlineStr"/>
+      <c r="S406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineWhiskySpiritsSG/</t>
+        </is>
+      </c>
+      <c r="T406" s="2" t="inlineStr"/>
+      <c r="U406" s="2" t="inlineStr"/>
+      <c r="V406" s="2" t="inlineStr"/>
+      <c r="W406" s="2" t="inlineStr">
+        <is>
+          <t>Rick</t>
+        </is>
+      </c>
+      <c r="X406" s="2" t="inlineStr">
+        <is>
+          <t>Founder And Resident Sommelier</t>
+        </is>
+      </c>
+      <c r="Y406" s="2" t="inlineStr"/>
+      <c r="Z406" s="2" t="inlineStr"/>
+      <c r="AA406" s="2" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>Our Wine Coterie Llp</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>Our Wine Coterie Llp</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>122470</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>39 Woodlands Close, Woodlands</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>737856</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>https://owc-eshop.com, https://www.ourwinecoterie.com</t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr"/>
+      <c r="K407" s="2" t="inlineStr"/>
+      <c r="L407" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M407" s="2" t="inlineStr"/>
+      <c r="N407" s="2" t="inlineStr">
+        <is>
+          <t>enquiry@ourwinecoterie.com</t>
+        </is>
+      </c>
+      <c r="O407" s="2" t="inlineStr"/>
+      <c r="P407" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q407" s="2" t="inlineStr">
+        <is>
+          <t>T18LL1895E</t>
+        </is>
+      </c>
+      <c r="R407" s="2" t="inlineStr"/>
+      <c r="S407" s="2" t="inlineStr"/>
+      <c r="T407" s="2" t="inlineStr"/>
+      <c r="U407" s="2" t="inlineStr"/>
+      <c r="V407" s="2" t="inlineStr"/>
+      <c r="W407" s="2" t="inlineStr">
+        <is>
+          <t>Samuel Koh</t>
+        </is>
+      </c>
+      <c r="X407" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y407" s="2" t="inlineStr"/>
+      <c r="Z407" s="2" t="inlineStr"/>
+      <c r="AA407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/samkohyn/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Singapore.xlsx
+++ b/BWI/bestwine_output/bestwine_Singapore.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA407"/>
+  <dimension ref="A1:AA412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -43964,6 +43964,475 @@
         </is>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>Finedrops Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>Finedrops Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>55904</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>66 Sungei Kadut Loop, Sungei Kadut</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>729503</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>https://finedrops.sg</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr"/>
+      <c r="K408" s="2" t="inlineStr"/>
+      <c r="L408" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M408" s="2" t="inlineStr"/>
+      <c r="N408" s="2" t="inlineStr">
+        <is>
+          <t>office@finedrops.sg</t>
+        </is>
+      </c>
+      <c r="O408" s="2" t="inlineStr"/>
+      <c r="P408" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q408" s="2" t="inlineStr">
+        <is>
+          <t>201806216W</t>
+        </is>
+      </c>
+      <c r="R408" s="2" t="inlineStr"/>
+      <c r="S408" s="2" t="inlineStr"/>
+      <c r="T408" s="2" t="inlineStr"/>
+      <c r="U408" s="2" t="inlineStr"/>
+      <c r="V408" s="2" t="inlineStr"/>
+      <c r="W408" s="2" t="inlineStr"/>
+      <c r="X408" s="2" t="inlineStr"/>
+      <c r="Y408" s="2" t="inlineStr"/>
+      <c r="Z408" s="2" t="inlineStr"/>
+      <c r="AA408" s="2" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>Hai Choo Wines &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>Hai Choo Wines &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>11804</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>48 Toh Guan Road East, Clementi</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>608586</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>https://hai-choo-wines-spirits.fairmart.app, https://hcwines.com</t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="inlineStr"/>
+      <c r="K409" s="2" t="inlineStr"/>
+      <c r="L409" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M409" s="2" t="inlineStr"/>
+      <c r="N409" s="2" t="inlineStr">
+        <is>
+          <t>sales@hcwines.com</t>
+        </is>
+      </c>
+      <c r="O409" s="2" t="inlineStr">
+        <is>
+          <t>+65 6515 6538</t>
+        </is>
+      </c>
+      <c r="P409" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q409" s="2" t="inlineStr">
+        <is>
+          <t>37556200A</t>
+        </is>
+      </c>
+      <c r="R409" s="2" t="inlineStr"/>
+      <c r="S409" s="2" t="inlineStr"/>
+      <c r="T409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winingwithhc/</t>
+        </is>
+      </c>
+      <c r="U409" s="2" t="inlineStr"/>
+      <c r="V409" s="2" t="inlineStr"/>
+      <c r="W409" s="2" t="inlineStr">
+        <is>
+          <t>Kelvin Tan</t>
+        </is>
+      </c>
+      <c r="X409" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y409" s="2" t="inlineStr"/>
+      <c r="Z409" s="2" t="inlineStr"/>
+      <c r="AA409" s="2" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/in/kelvin-tan-a040891</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>Hai Choo Wines &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>Hai Choo Wines &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>11804</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>48 Toh Guan Road East, Clementi</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>608586</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>https://hai-choo-wines-spirits.fairmart.app, https://hcwines.com</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr"/>
+      <c r="K410" s="2" t="inlineStr"/>
+      <c r="L410" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M410" s="2" t="inlineStr"/>
+      <c r="N410" s="2" t="inlineStr">
+        <is>
+          <t>sales@hcwines.com</t>
+        </is>
+      </c>
+      <c r="O410" s="2" t="inlineStr">
+        <is>
+          <t>+65 6515 6538</t>
+        </is>
+      </c>
+      <c r="P410" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q410" s="2" t="inlineStr">
+        <is>
+          <t>37556200A</t>
+        </is>
+      </c>
+      <c r="R410" s="2" t="inlineStr"/>
+      <c r="S410" s="2" t="inlineStr"/>
+      <c r="T410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winingwithhc/</t>
+        </is>
+      </c>
+      <c r="U410" s="2" t="inlineStr"/>
+      <c r="V410" s="2" t="inlineStr"/>
+      <c r="W410" s="2" t="inlineStr">
+        <is>
+          <t>Terence Goh</t>
+        </is>
+      </c>
+      <c r="X410" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y410" s="2" t="inlineStr"/>
+      <c r="Z410" s="2" t="inlineStr"/>
+      <c r="AA410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/terence-goh-478983163/</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>The Guild Collective Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>The Guild Collective Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>122487</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>Shaw Centre, 1 Scotts Road, Orchard</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>228208</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theguildcollective.com</t>
+        </is>
+      </c>
+      <c r="J411" s="2" t="inlineStr"/>
+      <c r="K411" s="2" t="inlineStr"/>
+      <c r="L411" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M411" s="2" t="inlineStr"/>
+      <c r="N411" s="2" t="inlineStr">
+        <is>
+          <t>hello@theguildcollective.com</t>
+        </is>
+      </c>
+      <c r="O411" s="2" t="inlineStr"/>
+      <c r="P411" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q411" s="2" t="inlineStr">
+        <is>
+          <t>201906364W</t>
+        </is>
+      </c>
+      <c r="R411" s="2" t="inlineStr"/>
+      <c r="S411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineWhiskySpiritsSG/</t>
+        </is>
+      </c>
+      <c r="T411" s="2" t="inlineStr"/>
+      <c r="U411" s="2" t="inlineStr"/>
+      <c r="V411" s="2" t="inlineStr"/>
+      <c r="W411" s="2" t="inlineStr">
+        <is>
+          <t>Rick</t>
+        </is>
+      </c>
+      <c r="X411" s="2" t="inlineStr">
+        <is>
+          <t>Founder And Resident Sommelier</t>
+        </is>
+      </c>
+      <c r="Y411" s="2" t="inlineStr"/>
+      <c r="Z411" s="2" t="inlineStr"/>
+      <c r="AA411" s="2" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>Our Wine Coterie Llp</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>Our Wine Coterie Llp</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>122470</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>39 Woodlands Close, Woodlands</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>737856</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>https://owc-eshop.com, https://www.ourwinecoterie.com</t>
+        </is>
+      </c>
+      <c r="J412" s="2" t="inlineStr"/>
+      <c r="K412" s="2" t="inlineStr"/>
+      <c r="L412" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="inlineStr"/>
+      <c r="N412" s="2" t="inlineStr">
+        <is>
+          <t>enquiry@ourwinecoterie.com</t>
+        </is>
+      </c>
+      <c r="O412" s="2" t="inlineStr"/>
+      <c r="P412" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q412" s="2" t="inlineStr">
+        <is>
+          <t>T18LL1895E</t>
+        </is>
+      </c>
+      <c r="R412" s="2" t="inlineStr"/>
+      <c r="S412" s="2" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
+      <c r="V412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="inlineStr">
+        <is>
+          <t>Samuel Koh</t>
+        </is>
+      </c>
+      <c r="X412" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y412" s="2" t="inlineStr"/>
+      <c r="Z412" s="2" t="inlineStr"/>
+      <c r="AA412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/samkohyn/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
